--- a/fastapi_app/excelAnalysis/8月可力洛销售数据分析报告.xlsx
+++ b/fastapi_app/excelAnalysis/8月可力洛销售数据分析报告.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/happyelements/Documents/my-project/my_python3_project/fastapi_app/excelAnalysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA942BF0-DE03-A04B-9F53-AA9A40AD995B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F179B07-A998-1F45-A49E-33B4613316A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
